--- a/all_sim/det_gemini_realset.xlsx
+++ b/all_sim/det_gemini_realset.xlsx
@@ -331,16 +331,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="17.6" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.5541666666666667</v>
+        <v>0.7770833333333333</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.5541666666666667</v>
+        <v>0.7770833333333333</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.5541666666666667</v>
+        <v>0.7770833333333333</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.5541666666666667</v>
+        <v>0.7770833333333333</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.5541666666666667</v>
+        <v>0.7770833333333333</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.5125</v>
+        <v>0.75625</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.5125</v>
+        <v>0.75625</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.5125</v>
+        <v>0.75625</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.7383333333333333</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.3966666666666666</v>
+        <v>0.6983333333333333</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.3966666666666666</v>
+        <v>0.6983333333333333</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.3966666666666666</v>
+        <v>0.6983333333333333</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.3966666666666666</v>
+        <v>0.6983333333333333</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.3966666666666666</v>
+        <v>0.6983333333333333</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.3966666666666666</v>
+        <v>0.6983333333333333</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.35666666666666663</v>
+        <v>0.6783333333333333</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.35666666666666663</v>
+        <v>0.6783333333333333</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.4458333333333333</v>
+        <v>0.7053728070175438</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8761904761904762</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8761904761904762</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8761904761904762</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8761904761904762</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8761904761904762</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8761904761904762</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8761904761904762</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8761904761904762</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8761904761904762</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8761904761904762</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.038461538461538464</v>
+        <v>0.31089743589743585</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.038461538461538464</v>
+        <v>0.31089743589743585</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.038461538461538464</v>
+        <v>0.31089743589743585</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.038461538461538464</v>
+        <v>0.31089743589743585</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.038461538461538464</v>
+        <v>0.31089743589743585</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.038461538461538464</v>
+        <v>0.31089743589743585</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.038461538461538464</v>
+        <v>0.31089743589743585</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.038461538461538464</v>
+        <v>0.31089743589743585</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.038461538461538464</v>
+        <v>0.31089743589743585</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.038461538461538464</v>
+        <v>0.31089743589743585</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.35885416666666675</v>
+        <v>0.6149109543010753</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.35885416666666675</v>
+        <v>0.6149109543010753</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.3560019841269842</v>
+        <v>0.6262768541324576</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.24548611111111113</v>
+        <v>0.5870287698412698</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.24548611111111113</v>
+        <v>0.5870287698412698</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.18732638888888892</v>
+        <v>0.5579489087301588</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.18732638888888892</v>
+        <v>0.5579489087301588</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.18177083333333333</v>
+        <v>0.555171130952381</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.1310763888888889</v>
+        <v>0.5078458867521367</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.13256448412698413</v>
+        <v>0.5085899343711844</v>
       </c>
     </row>
     <row r="6">
@@ -538,31 +538,31 @@
         <v>1.0</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.7738505747126436</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.7738505747126436</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.7738505747126436</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.7738505747126436</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.7738505747126436</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.7738505747126436</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.7738505747126436</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.7738505747126436</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.8663194444444444</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.7088293650793651</v>
+        <v>0.8544146825396826</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.6671626984126985</v>
+        <v>0.8335813492063493</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.6671626984126985</v>
+        <v>0.8335813492063493</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.8246527777777778</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.8246527777777778</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.8246527777777778</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.8246527777777778</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.8246527777777778</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.8246527777777778</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.262797619047619</v>
+        <v>0.6313988095238094</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.17291666666666666</v>
+        <v>0.5864583333333333</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.12708333333333333</v>
+        <v>0.5227253401360544</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.13124999999999998</v>
+        <v>0.5248086734693878</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.13124999999999998</v>
+        <v>0.5248086734693878</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.13124999999999998</v>
+        <v>0.5248086734693878</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.13124999999999998</v>
+        <v>0.5248086734693878</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.13124999999999998</v>
+        <v>0.5248086734693878</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.13124999999999998</v>
+        <v>0.5248086734693878</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.13124999999999998</v>
+        <v>0.5248086734693878</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.2523809523809524</v>
+        <v>0.5949404761904762</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.2523809523809524</v>
+        <v>0.5949404761904762</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.2523809523809524</v>
+        <v>0.5949404761904762</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.2523809523809524</v>
+        <v>0.5949404761904762</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.2523809523809524</v>
+        <v>0.5949404761904762</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.2523809523809524</v>
+        <v>0.5949404761904762</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.2523809523809524</v>
+        <v>0.5949404761904762</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.2523809523809524</v>
+        <v>0.5949404761904762</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.2523809523809524</v>
+        <v>0.5949404761904762</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.2523809523809524</v>
+        <v>0.5949404761904762</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.6277777777777779</v>
+        <v>0.8030193236714976</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.697530864197531</v>
+        <v>0.8161567364465916</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.6777777777777778</v>
+        <v>0.806280193236715</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.697530864197531</v>
+        <v>0.8161567364465916</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.697530864197531</v>
+        <v>0.8161567364465916</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.8100649350649352</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.8100649350649352</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.8100649350649352</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.8100649350649352</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.8100649350649352</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.5170833333333336</v>
+        <v>0.7442559523809524</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.48380050505050515</v>
+        <v>0.7276145382395383</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.48380050505050515</v>
+        <v>0.7276145382395383</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.43183080808080787</v>
+        <v>0.6865036393345216</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.550012626262626</v>
+        <v>0.7455945484254307</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.27626262626262627</v>
+        <v>0.5926767676767677</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.27626262626262627</v>
+        <v>0.5926767676767677</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.5816666666666668</v>
+        <v>0.7618478260869566</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.5816666666666668</v>
+        <v>0.7618478260869566</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.5816666666666668</v>
+        <v>0.7618478260869566</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.9555555555555557</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.9555555555555557</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.9555555555555557</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.9555555555555557</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.9555555555555557</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.9555555555555557</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.9555555555555557</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.9555555555555557</v>
+        <v>0.9777777777777779</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.46045918367346955</v>
+        <v>0.7150780766852196</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.27086167800453514</v>
+        <v>0.5827992600548991</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.27086167800453514</v>
+        <v>0.5827992600548991</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.27086167800453514</v>
+        <v>0.5827992600548991</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.2526077097505669</v>
+        <v>0.573672275927915</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.26530612244897955</v>
+        <v>0.5624776226279986</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.26530612244897955</v>
+        <v>0.5800214822771214</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.11607142857142858</v>
+        <v>0.48530844155844155</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.11607142857142858</v>
+        <v>0.48530844155844155</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.11607142857142858</v>
+        <v>0.48530844155844155</v>
       </c>
     </row>
     <row r="14">
@@ -834,31 +834,31 @@
         <v>1.0</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6447368421052632</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6447368421052632</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6447368421052632</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6447368421052632</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6447368421052632</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6447368421052632</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6447368421052632</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6447368421052632</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6447368421052632</v>
       </c>
     </row>
     <row r="15">
@@ -868,34 +868,34 @@
         </is>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.75</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.6025641025641026</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.6025641025641026</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.7243589743589743</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.7243589743589743</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.7243589743589743</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.7243589743589743</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.6066763425253991</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.45833333333333337</v>
+        <v>0.671474358974359</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.3055555555555555</v>
+        <v>0.613562091503268</v>
       </c>
     </row>
     <row r="16">

--- a/all_sim/det_gemini_realset.xlsx
+++ b/all_sim/det_gemini_realset.xlsx
@@ -331,16 +331,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="17.6" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.7770833333333333</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.7770833333333333</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.7770833333333333</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.7770833333333333</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.7770833333333333</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.75625</v>
+        <v>0.5125</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.75625</v>
+        <v>0.5125</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.75625</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.6983333333333333</v>
+        <v>0.3966666666666666</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.6983333333333333</v>
+        <v>0.3966666666666666</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.6983333333333333</v>
+        <v>0.3966666666666666</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.6983333333333333</v>
+        <v>0.3966666666666666</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.6983333333333333</v>
+        <v>0.3966666666666666</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.6983333333333333</v>
+        <v>0.3966666666666666</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.6783333333333333</v>
+        <v>0.35666666666666663</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.6783333333333333</v>
+        <v>0.35666666666666663</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.7053728070175438</v>
+        <v>0.4301900584795321</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.31089743589743585</v>
+        <v>0.022435897435897436</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.31089743589743585</v>
+        <v>0.022435897435897436</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.31089743589743585</v>
+        <v>0.022435897435897436</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.31089743589743585</v>
+        <v>0.022435897435897436</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.31089743589743585</v>
+        <v>0.022435897435897436</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.31089743589743585</v>
+        <v>0.022435897435897436</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.31089743589743585</v>
+        <v>0.022435897435897436</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.31089743589743585</v>
+        <v>0.022435897435897436</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.31089743589743585</v>
+        <v>0.022435897435897436</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.31089743589743585</v>
+        <v>0.022435897435897436</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.6149109543010753</v>
+        <v>0.3125504032258065</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.6149109543010753</v>
+        <v>0.3125504032258065</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.6262768541324576</v>
+        <v>0.31917419266557207</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.5870287698412698</v>
+        <v>0.2279513888888889</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.5870287698412698</v>
+        <v>0.2279513888888889</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.5579489087301588</v>
+        <v>0.17394593253968257</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.5579489087301588</v>
+        <v>0.17394593253968257</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.555171130952381</v>
+        <v>0.16878720238095238</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.5078458867521367</v>
+        <v>0.11595219017094018</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.5085899343711844</v>
+        <v>0.11726858211233211</v>
       </c>
     </row>
     <row r="6">
@@ -538,31 +538,31 @@
         <v>1.0</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8377777777777778</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.7738505747126436</v>
+        <v>0.5741379310344827</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.7738505747126436</v>
+        <v>0.5741379310344827</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.7738505747126436</v>
+        <v>0.5741379310344827</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.7738505747126436</v>
+        <v>0.5741379310344827</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.7738505747126436</v>
+        <v>0.5741379310344827</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.7738505747126436</v>
+        <v>0.5741379310344827</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.7738505747126436</v>
+        <v>0.5741379310344827</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.7738505747126436</v>
+        <v>0.5741379310344827</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.8663194444444444</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.8544146825396826</v>
+        <v>0.7088293650793651</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.8335813492063493</v>
+        <v>0.6671626984126985</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.8335813492063493</v>
+        <v>0.6671626984126985</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.8246527777777778</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.8246527777777778</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.8246527777777778</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.8246527777777778</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.8246527777777778</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.8246527777777778</v>
+        <v>0.6493055555555556</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.6313988095238094</v>
+        <v>0.262797619047619</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.5864583333333333</v>
+        <v>0.17291666666666666</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.5227253401360544</v>
+        <v>0.11670918367346939</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.5248086734693878</v>
+        <v>0.12053571428571427</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.5248086734693878</v>
+        <v>0.12053571428571427</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.5248086734693878</v>
+        <v>0.12053571428571427</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.5248086734693878</v>
+        <v>0.12053571428571427</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.5248086734693878</v>
+        <v>0.12053571428571427</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.5248086734693878</v>
+        <v>0.12053571428571427</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.5248086734693878</v>
+        <v>0.12053571428571427</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.5949404761904762</v>
+        <v>0.23660714285714285</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.5949404761904762</v>
+        <v>0.23660714285714285</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.5949404761904762</v>
+        <v>0.23660714285714285</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.5949404761904762</v>
+        <v>0.23660714285714285</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.5949404761904762</v>
+        <v>0.23660714285714285</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.5949404761904762</v>
+        <v>0.23660714285714285</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.5949404761904762</v>
+        <v>0.23660714285714285</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.5949404761904762</v>
+        <v>0.23660714285714285</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.5949404761904762</v>
+        <v>0.23660714285714285</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.5949404761904762</v>
+        <v>0.23660714285714285</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.8030193236714976</v>
+        <v>0.6141304347826088</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.8161567364465916</v>
+        <v>0.6520397208803007</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.806280193236715</v>
+        <v>0.6335748792270532</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.8161567364465916</v>
+        <v>0.6520397208803007</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.8161567364465916</v>
+        <v>0.6520397208803007</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.8100649350649352</v>
+        <v>0.6282467532467533</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.8100649350649352</v>
+        <v>0.6282467532467533</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.8100649350649352</v>
+        <v>0.6282467532467533</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.8100649350649352</v>
+        <v>0.6282467532467533</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.8100649350649352</v>
+        <v>0.6282467532467533</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.7442559523809524</v>
+        <v>0.502309523809524</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.7276145382395383</v>
+        <v>0.46997763347763355</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.7276145382395383</v>
+        <v>0.46997763347763355</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.6865036393345216</v>
+        <v>0.40642899584076037</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.7455945484254307</v>
+        <v>0.5176589423648245</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.5926767676767677</v>
+        <v>0.25114784205693297</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.5926767676767677</v>
+        <v>0.25114784205693297</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.7618478260869566</v>
+        <v>0.5479468599033818</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.7618478260869566</v>
+        <v>0.5479468599033818</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.7618478260869566</v>
+        <v>0.5479468599033818</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9555555555555557</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9555555555555557</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9555555555555557</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9555555555555557</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9555555555555557</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9555555555555557</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9555555555555557</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9555555555555557</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.7150780766852196</v>
+        <v>0.4465058750773038</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.5827992600548991</v>
+        <v>0.2423499224251104</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.5827992600548991</v>
+        <v>0.2423499224251104</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.5827992600548991</v>
+        <v>0.2423499224251104</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.573672275927915</v>
+        <v>0.22601742451366513</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.5624776226279986</v>
+        <v>0.22807017543859645</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.5800214822771214</v>
+        <v>0.23737916219119223</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.48530844155844155</v>
+        <v>0.09918831168831169</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.48530844155844155</v>
+        <v>0.09918831168831169</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.48530844155844155</v>
+        <v>0.09918831168831169</v>
       </c>
     </row>
     <row r="14">
@@ -834,31 +834,31 @@
         <v>1.0</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.6447368421052632</v>
+        <v>0.39473684210526316</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.6447368421052632</v>
+        <v>0.39473684210526316</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.6447368421052632</v>
+        <v>0.39473684210526316</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.6447368421052632</v>
+        <v>0.39473684210526316</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.6447368421052632</v>
+        <v>0.39473684210526316</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.6447368421052632</v>
+        <v>0.39473684210526316</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.6447368421052632</v>
+        <v>0.39473684210526316</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.6447368421052632</v>
+        <v>0.39473684210526316</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.6447368421052632</v>
+        <v>0.39473684210526316</v>
       </c>
     </row>
     <row r="15">
@@ -868,34 +868,34 @@
         </is>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5443786982248521</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.5330374753451677</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.5330374753451677</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.7243589743589743</v>
+        <v>0.4990138067061144</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.7243589743589743</v>
+        <v>0.4990138067061144</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.7243589743589743</v>
+        <v>0.4990138067061144</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.7243589743589743</v>
+        <v>0.4990138067061144</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.6066763425253991</v>
+        <v>0.2786647314949202</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.671474358974359</v>
+        <v>0.40544871794871795</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.613562091503268</v>
+        <v>0.2815904139433551</v>
       </c>
     </row>
     <row r="16">
